--- a/model_info/gpt_realset.xlsx
+++ b/model_info/gpt_realset.xlsx
@@ -393,7 +393,7 @@
         <v>0.7947180346357484</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.21510598783406007</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.18095238095238095</v>
+        <v>0.5576893052302888</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.24537029653405526</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.2236111111111111</v>
+        <v>0.5436237373737374</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.26683794723123094</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.12654320987654322</v>
+        <v>0.49508978675645343</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.7875138353197244</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.6616541353383458</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.7131889022778672</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.13233398208773048</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.12251984126984128</v>
+        <v>0.5612599206349207</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.38235294117647056</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.22370190829846018</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.06108452950558213</v>
+        <v>0.39467269953539974</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.07490026121050584</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.37629937629937626</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.41394173053393263</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.32613636363636367</v>
+        <v>0.5191287878787879</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.13071917044165374</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.40022302350427347</v>
       </c>
     </row>
     <row r="14">
@@ -1079,7 +1079,7 @@
         <v>0.2113778663963243</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.375</v>
+        <v>0.5056818181818181</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.21713622875752067</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.5841269841269842</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/gpt_realset.xlsx
+++ b/model_info/gpt_realset.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="7.700000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.7947180346357484</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.21510598783406007</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.5576893052302888</v>
+        <v>0.16908665105386417</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.24537029653405526</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.5436237373737374</v>
+        <v>0.19311868686868686</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.26683794723123094</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.49508978675645343</v>
+        <v>0.10928731762065096</v>
       </c>
     </row>
     <row r="5">
@@ -638,7 +638,7 @@
         <v>0.7875138353197244</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.6616541353383458</v>
+        <v>0.3834586466165414</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.7131889022778672</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.13233398208773048</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.5612599206349207</v>
+        <v>0.12251984126984128</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.0</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.38235294117647056</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.22370190829846018</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.39467269953539974</v>
+        <v>0.044485472574717425</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.07490026121050584</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.37629937629937626</v>
+        <v>0.05197505197505198</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.41394173053393263</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.5191287878787879</v>
+        <v>0.23224862258953172</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.13071917044165374</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.40022302350427347</v>
+        <v>0.024011752136752135</v>
       </c>
     </row>
     <row r="14">
@@ -1079,7 +1079,7 @@
         <v>0.2113778663963243</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.5056818181818181</v>
+        <v>0.23863636363636365</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.21713622875752067</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.5841269841269842</v>
+        <v>0.26666666666666666</v>
       </c>
     </row>
   </sheetData>
